--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-23.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-23.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261021" sheetId="1" r:id="R19daa92781a643e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261022" sheetId="1" r:id="R888986e1743c4f10"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10,7 +10,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="173">
   <x:si>
-    <x:t>Daily Holdings (%)  10/21/2026</x:t>
+    <x:t>Daily Holdings (%)  10/22/2026</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -52,19 +52,19 @@
     <x:t>BBG000BBJQV0</x:t>
   </x:si>
   <x:si>
-    <x:t>64,472,781</x:t>
+    <x:t>65,168,706</x:t>
   </x:si>
   <x:si>
     <x:t>Stock</x:t>
   </x:si>
   <x:si>
-    <x:t>$14,311,023,198.57</x:t>
+    <x:t>$13,829,451,100.26</x:t>
   </x:si>
   <x:si>
     <x:t> -- </x:t>
   </x:si>
   <x:si>
-    <x:t>20.56%</x:t>
+    <x:t>20.92%</x:t>
   </x:si>
   <x:si>
     <x:t>TSM</x:t>
@@ -76,13 +76,31 @@
     <x:t>BBG000BD8ZK0</x:t>
   </x:si>
   <x:si>
-    <x:t>15,405,635</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$6,653,539,700.15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.56%</x:t>
+    <x:t>15,571,928</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$6,421,084,510.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.72%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Broadcom Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG00KHY5S69</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11,371,300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,675,659,012.00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.56%</x:t>
   </x:si>
   <x:si>
     <x:t>AMD</x:t>
@@ -94,31 +112,13 @@
     <x:t>BBG000BBQCY0</x:t>
   </x:si>
   <x:si>
-    <x:t>6,918,432</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,823,955,735.04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.49%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AVGO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Broadcom Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG00KHY5S69</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11,249,584</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,800,109,475.20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.46%</x:t>
+    <x:t>6,993,114</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,552,012,394.02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.37%</x:t>
   </x:si>
   <x:si>
     <x:t>TXN</x:t>
@@ -130,13 +130,13 @@
     <x:t>BBG000BVV7G1</x:t>
   </x:si>
   <x:si>
-    <x:t>12,375,282</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,522,624,021.30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5.06%</x:t>
+    <x:t>12,509,175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,496,314,412.50</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.29%</x:t>
   </x:si>
   <x:si>
     <x:t>MU</x:t>
@@ -148,13 +148,13 @@
     <x:t>BBG000C5Z1S3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,507,744</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,204,920,460.48</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.61%</x:t>
+    <x:t>3,545,598</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,036,769,231.02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.59%</x:t>
   </x:si>
   <x:si>
     <x:t>ADI</x:t>
@@ -166,13 +166,31 @@
     <x:t>BBG000BB6G37</x:t>
   </x:si>
   <x:si>
-    <x:t>7,762,516</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,151,270,995.36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.53%</x:t>
+    <x:t>7,846,486</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$3,026,860,439.36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.58%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASML</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Asml Holding Nv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000K6MRN4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,896,279</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,959,219,230.66</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.48%</x:t>
   </x:si>
   <x:si>
     <x:t>MRVL</x:t>
@@ -184,28 +202,31 @@
     <x:t>BBG00ZXBJ153</x:t>
   </x:si>
   <x:si>
-    <x:t>12,862,841</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,148,308,963.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.52%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ASML</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Asml Holding Nv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000K6MRN4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,876,029</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$3,145,519,064.01</x:t>
+    <x:t>13,001,675</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,905,484,312.25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.40%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QCOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Qualcomm Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000CGC1X8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,533,119</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,684,588,956.77</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.06%</x:t>
   </x:si>
   <x:si>
     <x:t>KLAC</x:t>
@@ -217,13 +238,13 @@
     <x:t>BBG000BMTFR4</x:t>
   </x:si>
   <x:si>
-    <x:t>17,698,622</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,892,485,793.46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.16%</x:t>
+    <x:t>17,890,106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,644,694,369.98</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.00%</x:t>
   </x:si>
   <x:si>
     <x:t>INTC</x:t>
@@ -235,13 +256,13 @@
     <x:t>BBG000C0G1D1</x:t>
   </x:si>
   <x:si>
-    <x:t>30,471,090</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,832,592,526.40</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.07%</x:t>
+    <x:t>30,800,733</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,633,154,664.17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.98%</x:t>
   </x:si>
   <x:si>
     <x:t>AMAT</x:t>
@@ -253,31 +274,31 @@
     <x:t>BBG000BBPFB9</x:t>
   </x:si>
   <x:si>
-    <x:t>6,904,679</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,823,599,430.26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4.06%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>QCOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Qualcomm Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000CGC1X8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,366,880</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,734,689,964.80</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.93%</x:t>
+    <x:t>6,979,388</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,621,318,545.04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.97%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SKHY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sk Hynix Inc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG0238L5JS9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,346,010</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,415,986,056.90</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.66%</x:t>
   </x:si>
   <x:si>
     <x:t>LRCX</x:t>
@@ -289,31 +310,13 @@
     <x:t>BBG000BNFLM9</x:t>
   </x:si>
   <x:si>
-    <x:t>10,249,667</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,673,215,650.27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.84%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SKHY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sk Hynix Inc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG0238L5JS9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,150,098</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$2,600,001,538.50</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3.74%</x:t>
+    <x:t>10,360,556</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$2,384,481,963.40</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.61%</x:t>
   </x:si>
   <x:si>
     <x:t>CDNS</x:t>
@@ -325,13 +328,13 @@
     <x:t>BBG000C13CD9</x:t>
   </x:si>
   <x:si>
-    <x:t>4,411,723</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,438,530,518.61</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2.07%</x:t>
+    <x:t>4,459,459</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,380,871,479.35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.09%</x:t>
   </x:si>
   <x:si>
     <x:t>SNPS</x:t>
@@ -343,10 +346,10 @@
     <x:t>BBG000BSFRF3</x:t>
   </x:si>
   <x:si>
-    <x:t>3,107,814</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$1,402,214,598.66</x:t>
+    <x:t>3,141,429</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$1,327,190,923.92</x:t>
   </x:si>
   <x:si>
     <x:t>2.01%</x:t>
@@ -361,13 +364,31 @@
     <x:t>BBG000C30L48</x:t>
   </x:si>
   <x:si>
-    <x:t>670,638</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$860,643,158.16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.24%</x:t>
+    <x:t>677,901</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$791,740,914.93</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.20%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NXPI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nxp Semiconductors Nv</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG000BND699</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,280,632</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$780,101,483.28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.18%</x:t>
   </x:si>
   <x:si>
     <x:t>TER</x:t>
@@ -379,31 +400,31 @@
     <x:t>BBG000BV4DR6</x:t>
   </x:si>
   <x:si>
-    <x:t>2,380,825</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$822,551,229.25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.18%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NXPI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Nxp Semiconductors Nv</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG000BND699</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,245,532</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$786,587,135.52</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.13%</x:t>
+    <x:t>2,406,583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$743,032,501.25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.12%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arm Holdings Plc</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BBG01J1GXZF0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,989,088</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$628,007,388.80</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.95%</x:t>
   </x:si>
   <x:si>
     <x:t>ALAB</x:t>
@@ -415,31 +436,10 @@
     <x:t>BBG00TDKHW99</x:t>
   </x:si>
   <x:si>
-    <x:t>2,401,694</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$696,635,361.64</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.00%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arm Holdings Plc</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BBG01J1GXZF0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,957,093</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$670,047,702.87</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.96%</x:t>
+    <x:t>2,427,668</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$625,901,363.76</x:t>
   </x:si>
   <x:si>
     <x:t>STM</x:t>
@@ -451,10 +451,10 @@
     <x:t>BBG000BD4GX2</x:t>
   </x:si>
   <x:si>
-    <x:t>12,976,301</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$615,465,956.43</x:t>
+    <x:t>13,116,674</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$578,314,156.66</x:t>
   </x:si>
   <x:si>
     <x:t>0.88%</x:t>
@@ -469,13 +469,13 @@
     <x:t>BBG000BHCP19</x:t>
   </x:si>
   <x:si>
-    <x:t>7,624,845</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$588,256,791.75</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.85%</x:t>
+    <x:t>7,707,330</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$574,350,231.60</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.87%</x:t>
   </x:si>
   <x:si>
     <x:t>ON</x:t>
@@ -487,13 +487,13 @@
     <x:t>BBG000DV7MX4</x:t>
   </x:si>
   <x:si>
-    <x:t>4,696,690</x:t>
-  </x:si>
-  <x:si>
-    <x:t>$361,363,328.60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.52%</x:t>
+    <x:t>4,747,504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>$347,659,717.92</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.53%</x:t>
   </x:si>
   <x:si>
     <x:t>-USD CASH-</x:t>
@@ -502,16 +502,16 @@
     <x:t> </x:t>
   </x:si>
   <x:si>
-    <x:t>43,885,767</x:t>
+    <x:t>43,893,735</x:t>
   </x:si>
   <x:si>
     <x:t>Cash Bal</x:t>
   </x:si>
   <x:si>
-    <x:t>$43,885,766.77</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0.06%</x:t>
+    <x:t>$43,893,735.10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0.07%</x:t>
   </x:si>
   <x:si>
     <x:t>Other/Cash</x:t>
@@ -520,7 +520,7 @@
     <x:t>Cash</x:t>
   </x:si>
   <x:si>
-    <x:t>$-13,231,068.51</x:t>
+    <x:t>$-13,886,336.97</x:t>
   </x:si>
   <x:si>
     <x:t>-0.02%</x:t>
@@ -955,7 +955,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="I12" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9" ht="15" customHeight="1">
@@ -963,28 +963,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I13" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9" ht="15" customHeight="1">
@@ -992,28 +992,28 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H14" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I14" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9" ht="15" customHeight="1">
@@ -1021,28 +1021,28 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I15" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9" ht="15" customHeight="1">
@@ -1050,28 +1050,28 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H16" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I16" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9" ht="15" customHeight="1">
@@ -1079,28 +1079,28 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I17" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9" ht="15" customHeight="1">
@@ -1108,28 +1108,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H18" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I18" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:9" ht="15" customHeight="1">
@@ -1137,28 +1137,28 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="H19" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I19" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:9" ht="15" customHeight="1">
@@ -1166,28 +1166,28 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I20" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:9" ht="15" customHeight="1">
@@ -1195,28 +1195,28 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I21" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:9" ht="15" customHeight="1">
@@ -1224,28 +1224,28 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I22" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:9" ht="15" customHeight="1">
@@ -1253,28 +1253,28 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I23" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:9" ht="15" customHeight="1">
@@ -1282,28 +1282,28 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H24" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="I24" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:9" ht="15" customHeight="1">
@@ -1311,28 +1311,28 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="H25" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="I25" s="1" t="s">
         <x:v>138</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="H25" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I25" s="1" t="s">
-        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:9" ht="15" customHeight="1">

--- a/holdings_snapshot/SMH/SMH_holdings_2026-10-23.xlsx
+++ b/holdings_snapshot/SMH/SMH_holdings_2026-10-23.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261022" sheetId="1" r:id="R888986e1743c4f10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SMH_asof_20261022" sheetId="1" r:id="R3e459644951b441a"/>
   </x:sheets>
 </x:workbook>
 </file>
